--- a/Foundation of Data Analysis/Data-Exploration-Excel/Preparing-Data/Date-Functions/Date-Functions.xlsx
+++ b/Foundation of Data Analysis/Data-Exploration-Excel/Preparing-Data/Date-Functions/Date-Functions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DS-ML-COURSE\Foundation of Data Analysis\Data-Exploration-Excel\Preparing-Data\Date-Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CEDD13C0-5E6F-4AF3-B999-A9E50C000936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FA89AC2-877D-4A65-93AD-FE4C4406B0A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{2EEB75DE-CE81-449B-860C-C1A676E6A366}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Today Date</t>
   </si>
@@ -61,6 +61,15 @@
   </si>
   <si>
     <t>Remove the Year</t>
+  </si>
+  <si>
+    <t>Strat date</t>
+  </si>
+  <si>
+    <t>end date</t>
+  </si>
+  <si>
+    <t>Year differnce</t>
   </si>
 </sst>
 </file>
@@ -96,10 +105,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -414,22 +424,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D3C1D3E-370B-453D-BEFE-839E16E109A7}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.54296875" customWidth="1"/>
     <col min="3" max="3" width="17.7265625" customWidth="1"/>
+    <col min="5" max="5" width="17.90625" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="3">
+        <v>45140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <f ca="1">TODAY()</f>
         <v>46090</v>
@@ -438,26 +456,38 @@
         <f ca="1">A2+2</f>
         <v>46092</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="3">
+        <v>45506</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <f ca="1">NOW()</f>
-        <v>46090.51287337963</v>
+        <v>46090.533713194447</v>
       </c>
       <c r="C4" s="1">
         <f ca="1">A2-2</f>
         <v>46088</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
@@ -465,7 +495,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6">
         <f ca="1">DAY(A2)</f>
         <v>9</v>
@@ -475,7 +505,7 @@
         <v>46151</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -483,7 +513,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8">
         <f ca="1">MONTH(A2)</f>
         <v>3</v>
@@ -493,7 +523,7 @@
         <v>46031</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -501,7 +531,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10">
         <f ca="1">YEAR(A2)</f>
         <v>2026</v>
@@ -511,7 +541,7 @@
         <v>46821</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -519,7 +549,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <f ca="1">DATE(A10,A8,A6)</f>
         <v>46090</v>
